--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="1351">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,6 +391,9 @@
     <t>Coordination hospitalière de prélèvement d'organes et de tissus</t>
   </si>
   <si>
+    <t>Equipe pluriprofessionnelle de professionnels de santé, ayant pour mission d'organiser et de coordonner les dons d'organes et de tissus, d'assurer le lien entre les différents acteurs de la chaîne de don, de garantir le respect des procédures et des bonnes pratiques légales éthiques et techniques, d'organiser la prise en charge du donneur et d'accompagner les proches tout au long du processus de don.</t>
+  </si>
+  <si>
     <t>036</t>
   </si>
   <si>
@@ -2110,6 +2113,9 @@
     <t>Accompagnements pour vivre dans un logement</t>
   </si>
   <si>
+    <t>Vise à l'appropriation et à la maîtrise du logement par la personne accompagnée pour qu'elle se constituer son « chez-soi ». Les publics visés sont les suivants : handicap, personnes âgées, protection de l'enfance et grande précarité.</t>
+  </si>
+  <si>
     <t>299</t>
   </si>
   <si>
@@ -2122,6 +2128,9 @@
     <t>Accompagnements à la scolarisation</t>
   </si>
   <si>
+    <t>L'accompagnement consiste à aider l'enfant à être acteur de sa scolarité et à l'accompagner en milieu ordinaire, encourager l'implication des parents dans la scolarité de l'enfant, identifier et développer les ressources de l'ESSMS pour accompagner collectivement les parcours scolaires, s'inscrire dans la communauté éducative par des missions d'appui-ressource.</t>
+  </si>
+  <si>
     <t>301</t>
   </si>
   <si>
@@ -2152,7 +2161,7 @@
     <t>305</t>
   </si>
   <si>
-    <t>Accompagnements dans l'activité professionnelle</t>
+    <t>Accompagnements pour mener sa vie professionnelle</t>
   </si>
   <si>
     <t>306</t>
@@ -2179,6 +2188,9 @@
     <t>Accompagnements à la vie affective et sexuelle</t>
   </si>
   <si>
+    <t>Information et accompagnements à la vie affective et sexuelle (inclut l'entretien contraception / pré-IVG etc.)</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
@@ -2260,7 +2272,10 @@
     <t>322</t>
   </si>
   <si>
-    <t>Prestation de restauration (dont portage de repas)</t>
+    <t>Prestation de restauration (dont portage de repas à domicile)</t>
+  </si>
+  <si>
+    <t>Service de préparation à domicile ou de livraison à domicile de repas, sur un territoire.</t>
   </si>
   <si>
     <t>323</t>
@@ -2393,6 +2408,9 @@
   </si>
   <si>
     <t>Coordination plan d'aide</t>
+  </si>
+  <si>
+    <t>Gestion et coordination de l'ensemble des services de soutien et de soins nécessaires pour aider une personne à vivre de manière autonome et à répondre à ses besoins quotidiens. Cela inclut la planification, la coordination des différents services et prestataires, et l'ajustement continu du plan en fonction des besoins changeants de la personne.</t>
   </si>
   <si>
     <t>342</t>
@@ -4867,17 +4885,19 @@
       <c r="C36" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>125</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -4886,10 +4906,10 @@
         <v>49</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -4898,10 +4918,10 @@
         <v>49</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -4910,10 +4930,10 @@
         <v>49</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -4922,13 +4942,13 @@
         <v>49</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -4936,10 +4956,10 @@
         <v>49</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -4948,10 +4968,10 @@
         <v>49</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -4960,10 +4980,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -4972,13 +4992,13 @@
         <v>49</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
@@ -4986,10 +5006,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -4998,10 +5018,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -5010,10 +5030,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -5022,10 +5042,10 @@
         <v>49</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -5034,10 +5054,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -5046,10 +5066,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -5058,10 +5078,10 @@
         <v>49</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -5070,10 +5090,10 @@
         <v>49</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -5082,10 +5102,10 @@
         <v>49</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -5094,10 +5114,10 @@
         <v>49</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -5106,10 +5126,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -5118,10 +5138,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -5130,10 +5150,10 @@
         <v>49</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -5142,10 +5162,10 @@
         <v>49</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -5154,10 +5174,10 @@
         <v>49</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -5166,10 +5186,10 @@
         <v>49</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -5178,10 +5198,10 @@
         <v>49</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -5190,10 +5210,10 @@
         <v>49</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -5202,10 +5222,10 @@
         <v>49</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -5214,10 +5234,10 @@
         <v>49</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -5226,10 +5246,10 @@
         <v>49</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -5238,10 +5258,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -5250,10 +5270,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -5262,10 +5282,10 @@
         <v>49</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -5274,10 +5294,10 @@
         <v>49</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -5286,10 +5306,10 @@
         <v>49</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -5298,10 +5318,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -5310,10 +5330,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -5322,10 +5342,10 @@
         <v>49</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -5334,10 +5354,10 @@
         <v>49</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -5346,10 +5366,10 @@
         <v>49</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -5358,10 +5378,10 @@
         <v>49</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -5370,13 +5390,13 @@
         <v>49</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79">
@@ -5384,10 +5404,10 @@
         <v>49</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -5396,10 +5416,10 @@
         <v>49</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -5408,10 +5428,10 @@
         <v>49</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -5420,10 +5440,10 @@
         <v>49</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -5432,10 +5452,10 @@
         <v>49</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -5444,10 +5464,10 @@
         <v>49</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -5456,13 +5476,13 @@
         <v>49</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86">
@@ -5470,13 +5490,13 @@
         <v>49</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87">
@@ -5484,10 +5504,10 @@
         <v>49</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -5496,10 +5516,10 @@
         <v>49</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -5508,10 +5528,10 @@
         <v>49</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -5520,10 +5540,10 @@
         <v>49</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -5532,10 +5552,10 @@
         <v>49</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -5544,10 +5564,10 @@
         <v>49</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -5556,10 +5576,10 @@
         <v>49</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -5568,10 +5588,10 @@
         <v>49</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -5580,10 +5600,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -5592,10 +5612,10 @@
         <v>49</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -5604,10 +5624,10 @@
         <v>49</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -5616,10 +5636,10 @@
         <v>49</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -5628,10 +5648,10 @@
         <v>49</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -5640,13 +5660,13 @@
         <v>49</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101">
@@ -5654,10 +5674,10 @@
         <v>49</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -5666,13 +5686,13 @@
         <v>49</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103">
@@ -5680,13 +5700,13 @@
         <v>49</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104">
@@ -5694,10 +5714,10 @@
         <v>49</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -5706,13 +5726,13 @@
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106">
@@ -5720,13 +5740,13 @@
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107">
@@ -5734,13 +5754,13 @@
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="108">
@@ -5748,10 +5768,10 @@
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -5760,10 +5780,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -5772,10 +5792,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -5784,10 +5804,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -5796,10 +5816,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -5808,10 +5828,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -5820,10 +5840,10 @@
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -5832,10 +5852,10 @@
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -5844,10 +5864,10 @@
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -5856,10 +5876,10 @@
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -5868,13 +5888,13 @@
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="119">
@@ -5882,10 +5902,10 @@
         <v>49</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -5894,10 +5914,10 @@
         <v>49</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -5906,10 +5926,10 @@
         <v>49</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -5918,10 +5938,10 @@
         <v>49</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -5930,10 +5950,10 @@
         <v>49</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -5942,10 +5962,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -5954,10 +5974,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -5966,10 +5986,10 @@
         <v>49</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -5978,10 +5998,10 @@
         <v>49</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -5990,10 +6010,10 @@
         <v>49</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -6002,10 +6022,10 @@
         <v>49</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -6014,10 +6034,10 @@
         <v>49</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -6026,10 +6046,10 @@
         <v>49</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -6038,10 +6058,10 @@
         <v>49</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -6050,13 +6070,13 @@
         <v>49</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="134">
@@ -6064,10 +6084,10 @@
         <v>49</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -6076,10 +6096,10 @@
         <v>49</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -6088,13 +6108,13 @@
         <v>49</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="137">
@@ -6102,10 +6122,10 @@
         <v>49</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -6114,10 +6134,10 @@
         <v>49</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -6126,10 +6146,10 @@
         <v>49</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -6138,10 +6158,10 @@
         <v>49</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -6150,10 +6170,10 @@
         <v>49</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -6162,10 +6182,10 @@
         <v>49</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -6174,10 +6194,10 @@
         <v>49</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -6186,10 +6206,10 @@
         <v>49</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -6198,10 +6218,10 @@
         <v>49</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -6210,10 +6230,10 @@
         <v>49</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -6222,10 +6242,10 @@
         <v>49</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -6234,10 +6254,10 @@
         <v>49</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -6246,10 +6266,10 @@
         <v>49</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -6258,10 +6278,10 @@
         <v>49</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -6270,10 +6290,10 @@
         <v>49</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -6282,10 +6302,10 @@
         <v>49</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -6294,10 +6314,10 @@
         <v>49</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -6306,10 +6326,10 @@
         <v>49</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -6318,10 +6338,10 @@
         <v>49</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -6330,10 +6350,10 @@
         <v>49</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -6342,10 +6362,10 @@
         <v>49</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -6354,10 +6374,10 @@
         <v>49</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -6366,10 +6386,10 @@
         <v>49</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -6378,10 +6398,10 @@
         <v>49</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -6390,10 +6410,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -6402,10 +6422,10 @@
         <v>49</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -6414,10 +6434,10 @@
         <v>49</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -6426,10 +6446,10 @@
         <v>49</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -6438,13 +6458,13 @@
         <v>49</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="166">
@@ -6452,10 +6472,10 @@
         <v>49</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -6464,10 +6484,10 @@
         <v>49</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -6476,10 +6496,10 @@
         <v>49</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -6488,13 +6508,13 @@
         <v>49</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170">
@@ -6502,10 +6522,10 @@
         <v>49</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -6514,13 +6534,13 @@
         <v>49</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="172">
@@ -6528,10 +6548,10 @@
         <v>49</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -6540,13 +6560,13 @@
         <v>49</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174">
@@ -6554,10 +6574,10 @@
         <v>49</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -6566,10 +6586,10 @@
         <v>49</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -6578,10 +6598,10 @@
         <v>49</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -6590,10 +6610,10 @@
         <v>49</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -6602,7 +6622,7 @@
         <v>49</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>108</v>
@@ -6614,13 +6634,13 @@
         <v>49</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="180">
@@ -6628,13 +6648,13 @@
         <v>49</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181">
@@ -6642,10 +6662,10 @@
         <v>49</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -6654,10 +6674,10 @@
         <v>49</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -6666,10 +6686,10 @@
         <v>49</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -6678,10 +6698,10 @@
         <v>49</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -6690,10 +6710,10 @@
         <v>49</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -6702,10 +6722,10 @@
         <v>49</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -6714,13 +6734,13 @@
         <v>49</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188">
@@ -6728,13 +6748,13 @@
         <v>49</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189">
@@ -6742,13 +6762,13 @@
         <v>49</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190">
@@ -6756,13 +6776,13 @@
         <v>49</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191">
@@ -6770,13 +6790,13 @@
         <v>49</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192">
@@ -6784,13 +6804,13 @@
         <v>49</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193">
@@ -6798,13 +6818,13 @@
         <v>49</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="194">
@@ -6812,13 +6832,13 @@
         <v>49</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="195">
@@ -6826,10 +6846,10 @@
         <v>49</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -6838,13 +6858,13 @@
         <v>49</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="197">
@@ -6852,13 +6872,13 @@
         <v>49</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="198">
@@ -6866,10 +6886,10 @@
         <v>49</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -6878,13 +6898,13 @@
         <v>49</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="200">
@@ -6892,13 +6912,13 @@
         <v>49</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="201">
@@ -6906,13 +6926,13 @@
         <v>49</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="202">
@@ -6920,13 +6940,13 @@
         <v>49</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="203">
@@ -6934,10 +6954,10 @@
         <v>49</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -6946,10 +6966,10 @@
         <v>49</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -6958,10 +6978,10 @@
         <v>49</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -6970,10 +6990,10 @@
         <v>49</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -6982,10 +7002,10 @@
         <v>49</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -6994,10 +7014,10 @@
         <v>49</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -7006,10 +7026,10 @@
         <v>49</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -7018,10 +7038,10 @@
         <v>49</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -7030,10 +7050,10 @@
         <v>49</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -7042,10 +7062,10 @@
         <v>49</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -7054,10 +7074,10 @@
         <v>49</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -7066,10 +7086,10 @@
         <v>49</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -7078,10 +7098,10 @@
         <v>49</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -7090,10 +7110,10 @@
         <v>49</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -7102,10 +7122,10 @@
         <v>49</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -7114,10 +7134,10 @@
         <v>49</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -7126,10 +7146,10 @@
         <v>49</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -7138,10 +7158,10 @@
         <v>49</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -7150,10 +7170,10 @@
         <v>49</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -7162,10 +7182,10 @@
         <v>49</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -7174,10 +7194,10 @@
         <v>49</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -7186,10 +7206,10 @@
         <v>49</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -7198,10 +7218,10 @@
         <v>49</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -7210,10 +7230,10 @@
         <v>49</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -7222,13 +7242,13 @@
         <v>49</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D227" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="228">
@@ -7236,10 +7256,10 @@
         <v>49</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -7248,10 +7268,10 @@
         <v>49</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -7260,10 +7280,10 @@
         <v>49</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -7272,10 +7292,10 @@
         <v>49</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -7284,13 +7304,13 @@
         <v>49</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D232" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233">
@@ -7298,10 +7318,10 @@
         <v>49</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -7310,13 +7330,13 @@
         <v>49</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D234" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="235">
@@ -7324,13 +7344,13 @@
         <v>49</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D235" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="236">
@@ -7338,13 +7358,13 @@
         <v>49</v>
       </c>
       <c r="B236" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="D236" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="C236" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="D236" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="237">
@@ -7352,13 +7372,13 @@
         <v>49</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D237" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="238">
@@ -7366,13 +7386,13 @@
         <v>49</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D238" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="239">
@@ -7380,10 +7400,10 @@
         <v>49</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -7392,13 +7412,13 @@
         <v>49</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="241">
@@ -7406,10 +7426,10 @@
         <v>49</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -7418,13 +7438,13 @@
         <v>49</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D242" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="243">
@@ -7432,10 +7452,10 @@
         <v>49</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -7444,13 +7464,13 @@
         <v>49</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="245">
@@ -7458,10 +7478,10 @@
         <v>49</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -7470,13 +7490,13 @@
         <v>49</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D246" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="247">
@@ -7484,10 +7504,10 @@
         <v>49</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -7496,10 +7516,10 @@
         <v>49</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -7508,10 +7528,10 @@
         <v>49</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -7520,10 +7540,10 @@
         <v>49</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -7532,10 +7552,10 @@
         <v>49</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -7544,10 +7564,10 @@
         <v>49</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -7556,10 +7576,10 @@
         <v>49</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -7568,10 +7588,10 @@
         <v>49</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -7580,10 +7600,10 @@
         <v>49</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -7592,10 +7612,10 @@
         <v>49</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -7604,10 +7624,10 @@
         <v>49</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -7616,10 +7636,10 @@
         <v>49</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -7628,10 +7648,10 @@
         <v>49</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -7640,10 +7660,10 @@
         <v>49</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -7652,10 +7672,10 @@
         <v>49</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -7664,10 +7684,10 @@
         <v>49</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -7676,10 +7696,10 @@
         <v>49</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -7688,10 +7708,10 @@
         <v>49</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -7700,10 +7720,10 @@
         <v>49</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -7712,10 +7732,10 @@
         <v>49</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -7724,10 +7744,10 @@
         <v>49</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -7736,10 +7756,10 @@
         <v>49</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -7748,10 +7768,10 @@
         <v>49</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -7760,10 +7780,10 @@
         <v>49</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -7772,10 +7792,10 @@
         <v>49</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -7784,10 +7804,10 @@
         <v>49</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -7796,10 +7816,10 @@
         <v>49</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -7808,10 +7828,10 @@
         <v>49</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -7820,10 +7840,10 @@
         <v>49</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -7832,10 +7852,10 @@
         <v>49</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -7844,10 +7864,10 @@
         <v>49</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -7856,10 +7876,10 @@
         <v>49</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -7868,10 +7888,10 @@
         <v>49</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -7880,13 +7900,13 @@
         <v>49</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D280" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="281">
@@ -7894,10 +7914,10 @@
         <v>49</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -7906,13 +7926,13 @@
         <v>49</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D282" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="283">
@@ -7920,13 +7940,13 @@
         <v>49</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D283" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="284">
@@ -7934,10 +7954,10 @@
         <v>49</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -7946,10 +7966,10 @@
         <v>49</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -7958,10 +7978,10 @@
         <v>49</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -7970,10 +7990,10 @@
         <v>49</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -7982,13 +8002,13 @@
         <v>49</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D288" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="289">
@@ -7996,13 +8016,13 @@
         <v>49</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D289" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="290">
@@ -8010,10 +8030,10 @@
         <v>49</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -8022,13 +8042,13 @@
         <v>49</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D291" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="292">
@@ -8036,13 +8056,13 @@
         <v>49</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D292" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="293">
@@ -8050,13 +8070,13 @@
         <v>49</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D293" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="294">
@@ -8064,10 +8084,10 @@
         <v>49</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -8076,10 +8096,10 @@
         <v>49</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -8088,10 +8108,10 @@
         <v>49</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -8100,10 +8120,10 @@
         <v>49</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -8112,10 +8132,10 @@
         <v>49</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -8124,22 +8144,24 @@
         <v>49</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="D299" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="D299" t="s" s="2">
+        <v>699</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -8148,22 +8170,24 @@
         <v>49</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="D301" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="D301" t="s" s="2">
+        <v>704</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -8172,13 +8196,13 @@
         <v>49</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D303" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="304">
@@ -8186,10 +8210,10 @@
         <v>49</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -8198,10 +8222,10 @@
         <v>49</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -8210,10 +8234,10 @@
         <v>49</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -8222,10 +8246,10 @@
         <v>49</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -8234,10 +8258,10 @@
         <v>49</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -8246,10 +8270,10 @@
         <v>49</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -8258,22 +8282,24 @@
         <v>49</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="D310" s="2"/>
+        <v>723</v>
+      </c>
+      <c r="D310" t="s" s="2">
+        <v>724</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -8282,10 +8308,10 @@
         <v>49</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -8294,13 +8320,13 @@
         <v>49</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D313" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="314">
@@ -8308,13 +8334,13 @@
         <v>49</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="315">
@@ -8322,10 +8348,10 @@
         <v>49</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -8334,10 +8360,10 @@
         <v>49</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -8346,10 +8372,10 @@
         <v>49</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -8358,10 +8384,10 @@
         <v>49</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -8370,10 +8396,10 @@
         <v>49</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -8382,10 +8408,10 @@
         <v>49</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -8394,10 +8420,10 @@
         <v>49</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -8406,10 +8432,10 @@
         <v>49</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -8418,22 +8444,24 @@
         <v>49</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="D323" s="2"/>
+        <v>752</v>
+      </c>
+      <c r="D323" t="s" s="2">
+        <v>753</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -8442,10 +8470,10 @@
         <v>49</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -8454,13 +8482,13 @@
         <v>49</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D326" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="327">
@@ -8468,10 +8496,10 @@
         <v>49</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -8480,10 +8508,10 @@
         <v>49</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -8492,10 +8520,10 @@
         <v>49</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -8504,10 +8532,10 @@
         <v>49</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -8516,10 +8544,10 @@
         <v>49</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -8528,10 +8556,10 @@
         <v>49</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -8540,10 +8568,10 @@
         <v>49</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -8552,10 +8580,10 @@
         <v>49</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -8564,13 +8592,13 @@
         <v>49</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D335" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="336">
@@ -8578,13 +8606,13 @@
         <v>49</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D336" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="337">
@@ -8592,10 +8620,10 @@
         <v>49</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -8604,10 +8632,10 @@
         <v>49</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -8616,13 +8644,13 @@
         <v>49</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="D339" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="340">
@@ -8630,13 +8658,13 @@
         <v>49</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="341">
@@ -8644,13 +8672,13 @@
         <v>49</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D341" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
     </row>
     <row r="342">
@@ -8658,22 +8686,24 @@
         <v>49</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="D342" s="2"/>
+        <v>797</v>
+      </c>
+      <c r="D342" t="s" s="2">
+        <v>798</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -8682,10 +8712,10 @@
         <v>49</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -8694,10 +8724,10 @@
         <v>49</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -8706,10 +8736,10 @@
         <v>49</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -8718,10 +8748,10 @@
         <v>49</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -8730,13 +8760,13 @@
         <v>49</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D348" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="349">
@@ -8744,10 +8774,10 @@
         <v>49</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -8756,13 +8786,13 @@
         <v>49</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D350" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="351">
@@ -8770,10 +8800,10 @@
         <v>49</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -8782,10 +8812,10 @@
         <v>49</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -8794,10 +8824,10 @@
         <v>49</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -8806,10 +8836,10 @@
         <v>49</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -8818,10 +8848,10 @@
         <v>49</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -8830,10 +8860,10 @@
         <v>49</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -8842,10 +8872,10 @@
         <v>49</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -8854,10 +8884,10 @@
         <v>49</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -8866,10 +8896,10 @@
         <v>49</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -8878,10 +8908,10 @@
         <v>49</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -8890,10 +8920,10 @@
         <v>49</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -8902,13 +8932,13 @@
         <v>49</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="D362" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="363">
@@ -8916,10 +8946,10 @@
         <v>49</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -8928,10 +8958,10 @@
         <v>49</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -8940,10 +8970,10 @@
         <v>49</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -8952,10 +8982,10 @@
         <v>49</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -8964,10 +8994,10 @@
         <v>49</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -8976,13 +9006,13 @@
         <v>49</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D368" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="369">
@@ -8990,10 +9020,10 @@
         <v>49</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -9002,10 +9032,10 @@
         <v>49</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -9014,10 +9044,10 @@
         <v>49</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -9026,10 +9056,10 @@
         <v>49</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -9038,10 +9068,10 @@
         <v>49</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -9050,10 +9080,10 @@
         <v>49</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -9062,10 +9092,10 @@
         <v>49</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -9074,10 +9104,10 @@
         <v>49</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -9086,10 +9116,10 @@
         <v>49</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -9098,10 +9128,10 @@
         <v>49</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -9110,10 +9140,10 @@
         <v>49</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -9122,10 +9152,10 @@
         <v>49</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -9134,10 +9164,10 @@
         <v>49</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -9146,10 +9176,10 @@
         <v>49</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -9158,10 +9188,10 @@
         <v>49</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -9170,10 +9200,10 @@
         <v>49</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -9182,10 +9212,10 @@
         <v>49</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -9194,10 +9224,10 @@
         <v>49</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -9206,10 +9236,10 @@
         <v>49</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -9218,10 +9248,10 @@
         <v>49</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -9230,10 +9260,10 @@
         <v>49</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -9242,10 +9272,10 @@
         <v>49</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -9254,10 +9284,10 @@
         <v>49</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -9266,10 +9296,10 @@
         <v>49</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -9278,10 +9308,10 @@
         <v>49</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -9290,13 +9320,13 @@
         <v>49</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D394" t="s" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
     </row>
     <row r="395">
@@ -9304,13 +9334,13 @@
         <v>49</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D395" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="396">
@@ -9318,10 +9348,10 @@
         <v>49</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -9330,10 +9360,10 @@
         <v>49</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -9342,13 +9372,13 @@
         <v>49</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="D398" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="399">
@@ -9356,10 +9386,10 @@
         <v>49</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -9368,10 +9398,10 @@
         <v>49</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -9380,10 +9410,10 @@
         <v>49</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -9392,10 +9422,10 @@
         <v>49</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -9404,10 +9434,10 @@
         <v>49</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -9416,10 +9446,10 @@
         <v>49</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -9428,13 +9458,13 @@
         <v>49</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="D405" t="s" s="2">
-        <v>924</v>
+        <v>930</v>
       </c>
     </row>
     <row r="406">
@@ -9442,10 +9472,10 @@
         <v>49</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -9454,10 +9484,10 @@
         <v>49</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -9466,10 +9496,10 @@
         <v>49</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -9478,10 +9508,10 @@
         <v>49</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -9490,13 +9520,13 @@
         <v>49</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D410" t="s" s="2">
-        <v>935</v>
+        <v>941</v>
       </c>
     </row>
     <row r="411">
@@ -9504,13 +9534,13 @@
         <v>49</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="D411" t="s" s="2">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="412">
@@ -9518,10 +9548,10 @@
         <v>49</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -9530,10 +9560,10 @@
         <v>49</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -9542,10 +9572,10 @@
         <v>49</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -9554,10 +9584,10 @@
         <v>49</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -9566,10 +9596,10 @@
         <v>49</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -9578,10 +9608,10 @@
         <v>49</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -9590,10 +9620,10 @@
         <v>49</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -9602,10 +9632,10 @@
         <v>49</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -9614,10 +9644,10 @@
         <v>49</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -9626,10 +9656,10 @@
         <v>49</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -9638,10 +9668,10 @@
         <v>49</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -9650,10 +9680,10 @@
         <v>49</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -9662,10 +9692,10 @@
         <v>49</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -9674,10 +9704,10 @@
         <v>49</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -9686,10 +9716,10 @@
         <v>49</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -9698,10 +9728,10 @@
         <v>49</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -9710,10 +9740,10 @@
         <v>49</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -9722,10 +9752,10 @@
         <v>49</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -9734,10 +9764,10 @@
         <v>49</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -9746,10 +9776,10 @@
         <v>49</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -9758,10 +9788,10 @@
         <v>49</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -9770,10 +9800,10 @@
         <v>49</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -9782,10 +9812,10 @@
         <v>49</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -9794,13 +9824,13 @@
         <v>49</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D435" t="s" s="2">
-        <v>987</v>
+        <v>993</v>
       </c>
     </row>
     <row r="436">
@@ -9808,13 +9838,13 @@
         <v>49</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D436" t="s" s="2">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
     <row r="437">
@@ -9822,10 +9852,10 @@
         <v>49</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -9834,13 +9864,13 @@
         <v>49</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="D438" t="s" s="2">
-        <v>995</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="439">
@@ -9848,10 +9878,10 @@
         <v>49</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -9860,13 +9890,13 @@
         <v>49</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="D440" t="s" s="2">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="441">
@@ -9874,13 +9904,13 @@
         <v>49</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="D441" t="s" s="2">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="442">
@@ -9888,13 +9918,13 @@
         <v>49</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D442" t="s" s="2">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="443">
@@ -9902,13 +9932,13 @@
         <v>49</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="D443" t="s" s="2">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="444">
@@ -9916,13 +9946,13 @@
         <v>49</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D444" t="s" s="2">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="445">
@@ -9930,13 +9960,13 @@
         <v>49</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="D445" t="s" s="2">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="446">
@@ -9944,13 +9974,13 @@
         <v>49</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="D446" t="s" s="2">
-        <v>1018</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="447">
@@ -9958,13 +9988,13 @@
         <v>49</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D447" t="s" s="2">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="448">
@@ -9972,13 +10002,13 @@
         <v>49</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D448" t="s" s="2">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="449">
@@ -9986,13 +10016,13 @@
         <v>49</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="D449" t="s" s="2">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="450">
@@ -10000,13 +10030,13 @@
         <v>49</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D450" t="s" s="2">
-        <v>1030</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="451">
@@ -10014,13 +10044,13 @@
         <v>49</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D451" t="s" s="2">
-        <v>1033</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="452">
@@ -10028,13 +10058,13 @@
         <v>49</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D452" t="s" s="2">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="453">
@@ -10042,13 +10072,13 @@
         <v>49</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="D453" t="s" s="2">
-        <v>1039</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="454">
@@ -10056,10 +10086,10 @@
         <v>49</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -10068,13 +10098,13 @@
         <v>49</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D455" t="s" s="2">
-        <v>1044</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="456">
@@ -10082,13 +10112,13 @@
         <v>49</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="D456" t="s" s="2">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="457">
@@ -10096,13 +10126,13 @@
         <v>49</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D457" t="s" s="2">
-        <v>1049</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="458">
@@ -10110,10 +10140,10 @@
         <v>49</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D458" s="2"/>
     </row>
@@ -10122,13 +10152,13 @@
         <v>49</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D459" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="460">
@@ -10136,13 +10166,13 @@
         <v>49</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D460" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="461">
@@ -10150,13 +10180,13 @@
         <v>49</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D461" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="462">
@@ -10164,13 +10194,13 @@
         <v>49</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D462" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="463">
@@ -10178,13 +10208,13 @@
         <v>49</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D463" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="464">
@@ -10192,13 +10222,13 @@
         <v>49</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D464" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="465">
@@ -10206,13 +10236,13 @@
         <v>49</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D465" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="466">
@@ -10220,13 +10250,13 @@
         <v>49</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="D466" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="467">
@@ -10234,13 +10264,13 @@
         <v>49</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="D467" t="s" s="2">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="468">
@@ -10248,13 +10278,13 @@
         <v>49</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="D468" t="s" s="2">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="469">
@@ -10262,13 +10292,13 @@
         <v>49</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="D469" t="s" s="2">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="470">
@@ -10276,13 +10306,13 @@
         <v>49</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="D470" t="s" s="2">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="471">
@@ -10290,13 +10320,13 @@
         <v>49</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="D471" t="s" s="2">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="472">
@@ -10304,13 +10334,13 @@
         <v>49</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D472" t="s" s="2">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="473">
@@ -10318,13 +10348,13 @@
         <v>49</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="474">
@@ -10332,13 +10362,13 @@
         <v>49</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D474" t="s" s="2">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="475">
@@ -10346,13 +10376,13 @@
         <v>49</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D475" t="s" s="2">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="476">
@@ -10360,13 +10390,13 @@
         <v>49</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="D476" t="s" s="2">
-        <v>1093</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="477">
@@ -10374,13 +10404,13 @@
         <v>49</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D477" t="s" s="2">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="478">
@@ -10388,13 +10418,13 @@
         <v>49</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="D478" t="s" s="2">
-        <v>1099</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="479">
@@ -10402,13 +10432,13 @@
         <v>49</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="D479" t="s" s="2">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="480">
@@ -10416,13 +10446,13 @@
         <v>49</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D480" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="481">
@@ -10430,13 +10460,13 @@
         <v>49</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D481" t="s" s="2">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="482">
@@ -10444,13 +10474,13 @@
         <v>49</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D482" t="s" s="2">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="483">
@@ -10458,13 +10488,13 @@
         <v>49</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="D483" t="s" s="2">
-        <v>1113</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="484">
@@ -10472,13 +10502,13 @@
         <v>49</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="D484" t="s" s="2">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="485">
@@ -10486,13 +10516,13 @@
         <v>49</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="D485" t="s" s="2">
-        <v>1119</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="486">
@@ -10500,13 +10530,13 @@
         <v>49</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D486" t="s" s="2">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="487">
@@ -10514,13 +10544,13 @@
         <v>49</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="D487" t="s" s="2">
-        <v>1125</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="488">
@@ -10528,13 +10558,13 @@
         <v>49</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="D488" t="s" s="2">
-        <v>1128</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="489">
@@ -10542,13 +10572,13 @@
         <v>49</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="D489" t="s" s="2">
-        <v>1131</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="490">
@@ -10556,13 +10586,13 @@
         <v>49</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D490" t="s" s="2">
-        <v>1134</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="491">
@@ -10570,13 +10600,13 @@
         <v>49</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D491" t="s" s="2">
-        <v>1137</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="492">
@@ -10584,10 +10614,10 @@
         <v>49</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="D492" s="2"/>
     </row>
@@ -10596,13 +10626,13 @@
         <v>49</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="D493" t="s" s="2">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="494">
@@ -10610,13 +10640,13 @@
         <v>49</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D494" t="s" s="2">
-        <v>1145</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="495">
@@ -10624,13 +10654,13 @@
         <v>49</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D495" t="s" s="2">
-        <v>1148</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="496">
@@ -10638,13 +10668,13 @@
         <v>49</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="D496" t="s" s="2">
-        <v>1151</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="497">
@@ -10652,13 +10682,13 @@
         <v>49</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="D497" t="s" s="2">
-        <v>1154</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="498">
@@ -10666,13 +10696,13 @@
         <v>49</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="D498" t="s" s="2">
-        <v>1157</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="499">
@@ -10680,13 +10710,13 @@
         <v>49</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D499" t="s" s="2">
-        <v>1160</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="500">
@@ -10694,10 +10724,10 @@
         <v>49</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D500" s="2"/>
     </row>
@@ -10706,13 +10736,13 @@
         <v>49</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="D501" t="s" s="2">
-        <v>1165</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="502">
@@ -10720,13 +10750,13 @@
         <v>49</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="D502" t="s" s="2">
-        <v>1168</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="503">
@@ -10734,13 +10764,13 @@
         <v>49</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="D503" t="s" s="2">
-        <v>1171</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="504">
@@ -10748,13 +10778,13 @@
         <v>49</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="D504" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="505">
@@ -10762,13 +10792,13 @@
         <v>49</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="D505" t="s" s="2">
-        <v>1177</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="506">
@@ -10776,13 +10806,13 @@
         <v>49</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="D506" t="s" s="2">
-        <v>1180</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="507">
@@ -10790,13 +10820,13 @@
         <v>49</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="D507" t="s" s="2">
-        <v>1183</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="508">
@@ -10804,13 +10834,13 @@
         <v>49</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="D508" t="s" s="2">
-        <v>1186</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="509">
@@ -10818,13 +10848,13 @@
         <v>49</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="D509" t="s" s="2">
-        <v>1189</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="510">
@@ -10832,13 +10862,13 @@
         <v>49</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="D510" t="s" s="2">
-        <v>1192</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="511">
@@ -10846,13 +10876,13 @@
         <v>49</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="D511" t="s" s="2">
-        <v>1195</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="512">
@@ -10860,13 +10890,13 @@
         <v>49</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="D512" t="s" s="2">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="513">
@@ -10874,13 +10904,13 @@
         <v>49</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="D513" t="s" s="2">
-        <v>1201</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="514">
@@ -10888,10 +10918,10 @@
         <v>49</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="D514" s="2"/>
     </row>
@@ -10900,10 +10930,10 @@
         <v>49</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="D515" s="2"/>
     </row>
@@ -10912,10 +10942,10 @@
         <v>49</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D516" s="2"/>
     </row>
@@ -10924,10 +10954,10 @@
         <v>49</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="D517" s="2"/>
     </row>
@@ -10936,10 +10966,10 @@
         <v>49</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D518" s="2"/>
     </row>
@@ -10948,10 +10978,10 @@
         <v>49</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D519" s="2"/>
     </row>
@@ -10960,13 +10990,13 @@
         <v>49</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D520" t="s" s="2">
-        <v>1216</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="521">
@@ -10974,13 +11004,13 @@
         <v>49</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D521" t="s" s="2">
-        <v>1219</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="522">
@@ -10988,10 +11018,10 @@
         <v>49</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D522" s="2"/>
     </row>
@@ -11000,13 +11030,13 @@
         <v>49</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D523" t="s" s="2">
-        <v>1224</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="524">
@@ -11014,10 +11044,10 @@
         <v>49</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D524" s="2"/>
     </row>
@@ -11026,10 +11056,10 @@
         <v>49</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="D525" s="2"/>
     </row>
@@ -11038,10 +11068,10 @@
         <v>49</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -11050,10 +11080,10 @@
         <v>49</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -11062,13 +11092,13 @@
         <v>49</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D528" t="s" s="2">
-        <v>1235</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="529">
@@ -11076,13 +11106,13 @@
         <v>49</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D529" t="s" s="2">
-        <v>1238</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="530">
@@ -11090,13 +11120,13 @@
         <v>49</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D530" t="s" s="2">
-        <v>1241</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="531">
@@ -11104,13 +11134,13 @@
         <v>49</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="D531" t="s" s="2">
-        <v>1244</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="532">
@@ -11118,13 +11148,13 @@
         <v>49</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="D532" t="s" s="2">
-        <v>1247</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="533">
@@ -11132,13 +11162,13 @@
         <v>49</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="D533" t="s" s="2">
-        <v>1250</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="534">
@@ -11146,10 +11176,10 @@
         <v>49</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="D534" s="2"/>
     </row>
@@ -11158,10 +11188,10 @@
         <v>49</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -11170,13 +11200,13 @@
         <v>49</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="D536" t="s" s="2">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="537">
@@ -11184,13 +11214,13 @@
         <v>49</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D537" t="s" s="2">
-        <v>1260</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="538">
@@ -11198,13 +11228,13 @@
         <v>49</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D538" t="s" s="2">
-        <v>1263</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="539">
@@ -11212,13 +11242,13 @@
         <v>49</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D539" t="s" s="2">
-        <v>1266</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="540">
@@ -11226,13 +11256,13 @@
         <v>49</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="D540" t="s" s="2">
-        <v>1269</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="541">
@@ -11240,13 +11270,13 @@
         <v>49</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D541" t="s" s="2">
-        <v>1272</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="542">
@@ -11254,13 +11284,13 @@
         <v>49</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="D542" t="s" s="2">
-        <v>1275</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="543">
@@ -11268,13 +11298,13 @@
         <v>49</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="D543" t="s" s="2">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="544">
@@ -11282,13 +11312,13 @@
         <v>49</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="D544" t="s" s="2">
-        <v>1281</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="545">
@@ -11296,13 +11326,13 @@
         <v>49</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="D545" t="s" s="2">
-        <v>1284</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="546">
@@ -11310,10 +11340,10 @@
         <v>49</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -11322,13 +11352,13 @@
         <v>49</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="D547" t="s" s="2">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="548">
@@ -11336,10 +11366,10 @@
         <v>49</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -11348,10 +11378,10 @@
         <v>49</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -11360,13 +11390,13 @@
         <v>49</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="D550" t="s" s="2">
-        <v>1296</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="551">
@@ -11374,10 +11404,10 @@
         <v>49</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -11386,10 +11416,10 @@
         <v>49</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -11398,10 +11428,10 @@
         <v>49</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D553" s="2"/>
     </row>
@@ -11410,10 +11440,10 @@
         <v>49</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D554" s="2"/>
     </row>
@@ -11422,10 +11452,10 @@
         <v>49</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="D555" s="2"/>
     </row>
@@ -11434,10 +11464,10 @@
         <v>49</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="D556" s="2"/>
     </row>
@@ -11446,10 +11476,10 @@
         <v>49</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D557" s="2"/>
     </row>
@@ -11458,10 +11488,10 @@
         <v>49</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="D558" s="2"/>
     </row>
@@ -11470,10 +11500,10 @@
         <v>49</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="D559" s="2"/>
     </row>
@@ -11482,10 +11512,10 @@
         <v>49</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D560" s="2"/>
     </row>
@@ -11494,10 +11524,10 @@
         <v>49</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="D561" s="2"/>
     </row>
@@ -11506,10 +11536,10 @@
         <v>49</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="D562" s="2"/>
     </row>
@@ -11518,10 +11548,10 @@
         <v>49</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="D563" s="2"/>
     </row>
@@ -11530,10 +11560,10 @@
         <v>49</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="D564" s="2"/>
     </row>
@@ -11542,10 +11572,10 @@
         <v>49</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="D565" s="2"/>
     </row>
@@ -11554,10 +11584,10 @@
         <v>49</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="D566" s="2"/>
     </row>
@@ -11566,10 +11596,10 @@
         <v>49</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="D567" s="2"/>
     </row>
@@ -11578,10 +11608,10 @@
         <v>49</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="D568" s="2"/>
     </row>
@@ -11590,10 +11620,10 @@
         <v>49</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="D569" s="2"/>
     </row>
@@ -11602,10 +11632,10 @@
         <v>49</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="D570" s="2"/>
     </row>
@@ -11614,10 +11644,10 @@
         <v>49</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="D571" s="2"/>
     </row>
@@ -11626,10 +11656,10 @@
         <v>49</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="D572" s="2"/>
     </row>
@@ -11638,10 +11668,10 @@
         <v>49</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="D573" s="2"/>
     </row>
@@ -11650,10 +11680,10 @@
         <v>49</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="D574" s="2"/>
     </row>
